--- a/epm/input/data_sapp_feb26/trade/pNewTransmission.xlsx
+++ b/epm/input/data_sapp_feb26/trade/pNewTransmission.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wb590499\Documents\Projects\EPM\epm\input\data_sapp_feb26\trade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B4F8BFDA-2F85-4436-B395-28DF3C5D52B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C06005-C784-4025-B2C4-73F1C3B69FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{12EFF4C2-4447-4578-A234-0367EAF46FDD}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{12EFF4C2-4447-4578-A234-0367EAF46FDD}"/>
   </bookViews>
   <sheets>
     <sheet name="pNewTransmission" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="23">
   <si>
     <t>From</t>
   </si>
@@ -949,8 +962,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EF5CF9C-E879-4280-8278-ABB1A1973FA7}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -998,7 +1020,7 @@
         <v>103</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -1024,7 +1046,7 @@
         <v>305.73099999999999</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -1050,7 +1072,7 @@
         <v>246.80459999999999</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1076,7 +1098,7 @@
         <v>250</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1084,28 +1106,28 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F6">
-        <v>134.11000000000001</v>
+        <v>250</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
@@ -1113,22 +1135,22 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F7">
-        <v>167.52</v>
+        <v>134.11000000000001</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
         <v>21</v>
@@ -1136,28 +1158,28 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
       <c r="C8">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F8">
-        <v>180</v>
+        <v>167.52</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
@@ -1165,22 +1187,22 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F9">
-        <v>107.184</v>
+        <v>180</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1188,25 +1210,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F10">
-        <v>180</v>
+        <v>107.184</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -1214,28 +1236,28 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>925</v>
+        <v>400</v>
       </c>
       <c r="F11">
-        <v>142.6</v>
+        <v>180</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
@@ -1243,36 +1265,36 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C12">
-        <v>2035</v>
+        <v>2028</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>300</v>
+        <v>925</v>
       </c>
       <c r="F12">
-        <v>344.52</v>
+        <v>142.6</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1281,10 +1303,10 @@
         <v>300</v>
       </c>
       <c r="F13">
-        <v>128.51499999999999</v>
+        <v>344.52</v>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1292,13 +1314,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1307,10 +1329,10 @@
         <v>300</v>
       </c>
       <c r="F14">
-        <v>150.02000000000001</v>
+        <v>128.51499999999999</v>
       </c>
       <c r="G14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -1321,7 +1343,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>2035</v>
@@ -1336,7 +1358,7 @@
         <v>150.02000000000001</v>
       </c>
       <c r="G15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1344,10 +1366,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <v>2035</v>
@@ -1359,10 +1381,10 @@
         <v>300</v>
       </c>
       <c r="F16">
-        <v>170</v>
+        <v>150.02000000000001</v>
       </c>
       <c r="G16">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -1373,22 +1395,22 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>410</v>
+        <v>300</v>
       </c>
       <c r="F17">
-        <v>68.352000000000004</v>
+        <v>170</v>
       </c>
       <c r="G17">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -1399,25 +1421,25 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="F18">
-        <v>315</v>
+        <v>68.352000000000004</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
@@ -1425,24 +1447,50 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
+        <v>500</v>
+      </c>
+      <c r="F19">
+        <v>315</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>2033</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
         <v>400</v>
       </c>
-      <c r="F19">
+      <c r="F20">
         <v>340</v>
       </c>
-      <c r="G19">
-        <v>30</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20" t="s">
         <v>22</v>
       </c>
     </row>
